--- a/output/capital.xlsx
+++ b/output/capital.xlsx
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8712</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="61">
